--- a/backend/{templates}/financial-statements-{model}.xlsx
+++ b/backend/{templates}/financial-statements-{model}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="539" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C07145B-0934-4BB5-A944-788E7C5EDF07}"/>
+  <xr:revisionPtr revIDLastSave="551" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B11719D4-7857-4CF5-A008-581E1FBC9F1B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="E-Cooking" sheetId="2" r:id="rId1"/>
@@ -611,6 +611,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -878,8 +882,8 @@
   <dimension ref="A1:AS121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" customWidth="1"/>
-    <col min="2" max="2" width="39.08984375" customWidth="1"/>
+    <col min="1" max="1" width="28.08984375" customWidth="1"/>
+    <col min="2" max="2" width="15.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
@@ -17469,8 +17473,8 @@
   <dimension ref="A1:AS121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="63.08984375" customWidth="1"/>
+    <col min="1" max="1" width="29.08984375" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
@@ -34060,8 +34064,8 @@
   <dimension ref="A1:AS121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.26953125" customWidth="1"/>
-    <col min="2" max="2" width="37.08984375" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">
@@ -50652,8 +50656,8 @@
   <dimension ref="A1:AS121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.1796875" customWidth="1"/>
-    <col min="2" max="2" width="63.08984375" customWidth="1"/>
+    <col min="1" max="1" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="15.5" x14ac:dyDescent="0.35">

--- a/backend/{templates}/financial-statements-{model}.xlsx
+++ b/backend/{templates}/financial-statements-{model}.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="555" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74257CA7-F20E-40C0-821E-E093AE44EDF2}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A84C2DA7-BAC2-46F8-9F9B-D92693233714}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="E-Cooking" sheetId="2" r:id="rId1"/>
-    <sheet name="Electricity" sheetId="6" r:id="rId2"/>
-    <sheet name="Electricity (Low access)" sheetId="5" r:id="rId3"/>
+    <sheet name="Electricity (Only E-Cooking)" sheetId="2" r:id="rId1"/>
+    <sheet name="Electricity &amp; E-Cooking" sheetId="6" r:id="rId2"/>
+    <sheet name="Electricity (Just access)" sheetId="5" r:id="rId3"/>
     <sheet name="LPG" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>

--- a/backend/{templates}/financial-statements-{model}.xlsx
+++ b/backend/{templates}/financial-statements-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="615" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{566D07C0-C7EF-4F51-A71F-7202AFC23DF0}"/>
+  <xr:revisionPtr revIDLastSave="642" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{821C7D91-175C-49B4-821B-02E1A416345B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity (Only E-Cooking)" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="101">
   <si>
     <t>Units</t>
   </si>
@@ -581,10 +581,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -866,8 +862,8 @@
       <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>1</v>
+      <c r="D1" s="9">
+        <v>2020</v>
       </c>
       <c r="E1" s="9">
         <v>2021</v>
@@ -6092,8 +6088,8 @@
       <c r="C40" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>1</v>
+      <c r="D40" s="9">
+        <v>2020</v>
       </c>
       <c r="E40" s="9">
         <v>2021</v>
@@ -8772,8 +8768,8 @@
       <c r="C60" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>1</v>
+      <c r="D60" s="9">
+        <v>2020</v>
       </c>
       <c r="E60" s="9">
         <v>2021</v>
@@ -11318,8 +11314,8 @@
       <c r="C79" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>1</v>
+      <c r="D79" s="9">
+        <v>2020</v>
       </c>
       <c r="E79" s="9">
         <v>2021</v>
@@ -12256,8 +12252,8 @@
       <c r="C86" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>1</v>
+      <c r="D86" s="9">
+        <v>2020</v>
       </c>
       <c r="E86" s="9">
         <v>2021</v>
@@ -13462,8 +13458,8 @@
       <c r="C95" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D95" s="9" t="s">
-        <v>1</v>
+      <c r="D95" s="9">
+        <v>2020</v>
       </c>
       <c r="E95" s="9">
         <v>2021</v>
@@ -14266,8 +14262,8 @@
       <c r="C101" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>1</v>
+      <c r="D101" s="9">
+        <v>2020</v>
       </c>
       <c r="E101" s="9">
         <v>2021</v>
@@ -16022,8 +16018,8 @@
       <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>1</v>
+      <c r="D1" s="9">
+        <v>2020</v>
       </c>
       <c r="E1" s="9">
         <v>2021</v>
@@ -21248,8 +21244,8 @@
       <c r="C40" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>1</v>
+      <c r="D40" s="9">
+        <v>2020</v>
       </c>
       <c r="E40" s="9">
         <v>2021</v>
@@ -23928,8 +23924,8 @@
       <c r="C60" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>1</v>
+      <c r="D60" s="9">
+        <v>2020</v>
       </c>
       <c r="E60" s="9">
         <v>2021</v>
@@ -26474,8 +26470,8 @@
       <c r="C79" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>1</v>
+      <c r="D79" s="9">
+        <v>2020</v>
       </c>
       <c r="E79" s="9">
         <v>2021</v>
@@ -27412,8 +27408,8 @@
       <c r="C86" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>1</v>
+      <c r="D86" s="9">
+        <v>2020</v>
       </c>
       <c r="E86" s="9">
         <v>2021</v>
@@ -28618,8 +28614,8 @@
       <c r="C95" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D95" s="9" t="s">
-        <v>1</v>
+      <c r="D95" s="9">
+        <v>2020</v>
       </c>
       <c r="E95" s="9">
         <v>2021</v>
@@ -29422,8 +29418,8 @@
       <c r="C101" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>1</v>
+      <c r="D101" s="9">
+        <v>2020</v>
       </c>
       <c r="E101" s="9">
         <v>2021</v>
@@ -31178,8 +31174,8 @@
       <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>1</v>
+      <c r="D1" s="9">
+        <v>2020</v>
       </c>
       <c r="E1" s="9">
         <v>2021</v>
@@ -36404,8 +36400,8 @@
       <c r="C40" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>1</v>
+      <c r="D40" s="9">
+        <v>2020</v>
       </c>
       <c r="E40" s="9">
         <v>2021</v>
@@ -39084,8 +39080,8 @@
       <c r="C60" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>1</v>
+      <c r="D60" s="9">
+        <v>2020</v>
       </c>
       <c r="E60" s="9">
         <v>2021</v>
@@ -41630,8 +41626,8 @@
       <c r="C79" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>1</v>
+      <c r="D79" s="9">
+        <v>2020</v>
       </c>
       <c r="E79" s="9">
         <v>2021</v>
@@ -42568,8 +42564,8 @@
       <c r="C86" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>1</v>
+      <c r="D86" s="9">
+        <v>2020</v>
       </c>
       <c r="E86" s="9">
         <v>2021</v>
@@ -43774,8 +43770,8 @@
       <c r="C95" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D95" s="9" t="s">
-        <v>1</v>
+      <c r="D95" s="9">
+        <v>2020</v>
       </c>
       <c r="E95" s="9">
         <v>2021</v>
@@ -44578,8 +44574,8 @@
       <c r="C101" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>1</v>
+      <c r="D101" s="9">
+        <v>2020</v>
       </c>
       <c r="E101" s="9">
         <v>2021</v>
@@ -46479,8 +46475,8 @@
       <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>1</v>
+      <c r="D1" s="9">
+        <v>2020</v>
       </c>
       <c r="E1" s="9">
         <v>2021</v>
@@ -51705,8 +51701,8 @@
       <c r="C40" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>1</v>
+      <c r="D40" s="9">
+        <v>2020</v>
       </c>
       <c r="E40" s="9">
         <v>2021</v>
@@ -54385,8 +54381,8 @@
       <c r="C60" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>1</v>
+      <c r="D60" s="9">
+        <v>2020</v>
       </c>
       <c r="E60" s="9">
         <v>2021</v>
@@ -56931,8 +56927,8 @@
       <c r="C79" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>1</v>
+      <c r="D79" s="9">
+        <v>2020</v>
       </c>
       <c r="E79" s="9">
         <v>2021</v>
@@ -57869,8 +57865,8 @@
       <c r="C86" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>1</v>
+      <c r="D86" s="9">
+        <v>2020</v>
       </c>
       <c r="E86" s="9">
         <v>2021</v>
@@ -59879,8 +59875,8 @@
       <c r="C101" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>1</v>
+      <c r="D101" s="9">
+        <v>2020</v>
       </c>
       <c r="E101" s="9">
         <v>2021</v>

--- a/backend/{templates}/financial-statements-{model}.xlsx
+++ b/backend/{templates}/financial-statements-{model}.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarr\OneDrive\Escritorio\IIT\CC-WBT\backend\{templates}\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="697" documentId="10_ncr:20000_{4F2B366B-AA2F-4F18-863E-957538EF6F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B581C11-0ADE-4F24-BC29-A3A1BB87B580}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20584A10-DDC8-4319-9C8C-8E497BC025D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity (Only E-Cooking)" sheetId="2" r:id="rId1"/>
@@ -553,7 +553,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -566,10 +566,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -837,7 +833,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99682AE1-5334-4A99-9652-64DF807A4E7D}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:AR113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.08984375" customWidth="1"/>
     <col min="2" max="2" width="15.90625" customWidth="1"/>
@@ -2319,7 +2315,7 @@
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>3</v>
@@ -2453,7 +2449,7 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>6</v>
@@ -2587,7 +2583,7 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>10</v>
@@ -2721,7 +2717,7 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>3</v>
@@ -2855,7 +2851,7 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>6</v>
@@ -2989,7 +2985,7 @@
     </row>
     <row r="17" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>10</v>
@@ -3123,7 +3119,7 @@
     </row>
     <row r="18" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>3</v>
@@ -3257,7 +3253,7 @@
     </row>
     <row r="19" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>6</v>
@@ -3391,7 +3387,7 @@
     </row>
     <row r="20" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>10</v>
@@ -3524,10 +3520,10 @@
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -3658,14 +3654,14 @@
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>6</v>
+      <c r="A22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D22" s="18">
         <v>0</v>
@@ -3792,8 +3788,8 @@
       </c>
     </row>
     <row r="23" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>13</v>
+      <c r="A23" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>10</v>
@@ -3926,14 +3922,14 @@
       </c>
     </row>
     <row r="24" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>3</v>
+      <c r="A24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" s="18">
         <v>0</v>
@@ -4061,7 +4057,7 @@
     </row>
     <row r="25" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>3</v>
@@ -4195,7 +4191,7 @@
     </row>
     <row r="26" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>10</v>
@@ -4203,407 +4199,407 @@
       <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="18">
-        <v>0</v>
-      </c>
-      <c r="E26" s="18">
-        <v>0</v>
-      </c>
-      <c r="F26" s="18">
-        <v>0</v>
-      </c>
-      <c r="G26" s="18">
-        <v>0</v>
-      </c>
-      <c r="H26" s="18">
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="18">
-        <v>0</v>
-      </c>
-      <c r="K26" s="18">
-        <v>0</v>
-      </c>
-      <c r="L26" s="18">
-        <v>0</v>
-      </c>
-      <c r="M26" s="18">
-        <v>0</v>
-      </c>
-      <c r="N26" s="18">
-        <v>0</v>
-      </c>
-      <c r="O26" s="18">
-        <v>0</v>
-      </c>
-      <c r="P26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="18">
-        <v>0</v>
-      </c>
-      <c r="R26" s="18">
-        <v>0</v>
-      </c>
-      <c r="S26" s="18">
-        <v>0</v>
-      </c>
-      <c r="T26" s="18">
-        <v>0</v>
-      </c>
-      <c r="U26" s="18">
-        <v>0</v>
-      </c>
-      <c r="V26" s="18">
-        <v>0</v>
-      </c>
-      <c r="W26" s="18">
-        <v>0</v>
-      </c>
-      <c r="X26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="18">
+      <c r="D26" s="19">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
+        <v>0</v>
+      </c>
+      <c r="O26" s="19">
+        <v>0</v>
+      </c>
+      <c r="P26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="19">
+        <v>0</v>
+      </c>
+      <c r="R26" s="19">
+        <v>0</v>
+      </c>
+      <c r="S26" s="19">
+        <v>0</v>
+      </c>
+      <c r="T26" s="19">
+        <v>0</v>
+      </c>
+      <c r="U26" s="19">
+        <v>0</v>
+      </c>
+      <c r="V26" s="19">
+        <v>0</v>
+      </c>
+      <c r="W26" s="19">
+        <v>0</v>
+      </c>
+      <c r="X26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR26" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>10</v>
+      <c r="A27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0</v>
-      </c>
-      <c r="E27" s="18">
-        <v>0</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-      <c r="G27" s="18">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <v>0</v>
-      </c>
-      <c r="J27" s="18">
-        <v>0</v>
-      </c>
-      <c r="K27" s="18">
-        <v>0</v>
-      </c>
-      <c r="L27" s="18">
-        <v>0</v>
-      </c>
-      <c r="M27" s="18">
-        <v>0</v>
-      </c>
-      <c r="N27" s="18">
-        <v>0</v>
-      </c>
-      <c r="O27" s="18">
-        <v>0</v>
-      </c>
-      <c r="P27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
-        <v>0</v>
-      </c>
-      <c r="S27" s="18">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18">
-        <v>0</v>
-      </c>
-      <c r="U27" s="18">
-        <v>0</v>
-      </c>
-      <c r="V27" s="18">
-        <v>0</v>
-      </c>
-      <c r="W27" s="18">
-        <v>0</v>
-      </c>
-      <c r="X27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="18">
+        <v>1</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19">
+        <v>0</v>
+      </c>
+      <c r="P27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>0</v>
+      </c>
+      <c r="R27" s="19">
+        <v>0</v>
+      </c>
+      <c r="S27" s="19">
+        <v>0</v>
+      </c>
+      <c r="T27" s="19">
+        <v>0</v>
+      </c>
+      <c r="U27" s="19">
+        <v>0</v>
+      </c>
+      <c r="V27" s="19">
+        <v>0</v>
+      </c>
+      <c r="W27" s="19">
+        <v>0</v>
+      </c>
+      <c r="X27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>15</v>
+      <c r="A28" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18">
-        <v>0</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-      <c r="G28" s="18">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18">
-        <v>0</v>
-      </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="18">
-        <v>0</v>
-      </c>
-      <c r="K28" s="18">
-        <v>0</v>
-      </c>
-      <c r="L28" s="18">
-        <v>0</v>
-      </c>
-      <c r="M28" s="18">
-        <v>0</v>
-      </c>
-      <c r="N28" s="18">
-        <v>0</v>
-      </c>
-      <c r="O28" s="18">
-        <v>0</v>
-      </c>
-      <c r="P28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>0</v>
-      </c>
-      <c r="R28" s="18">
-        <v>0</v>
-      </c>
-      <c r="S28" s="18">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18">
-        <v>0</v>
-      </c>
-      <c r="U28" s="18">
-        <v>0</v>
-      </c>
-      <c r="V28" s="18">
-        <v>0</v>
-      </c>
-      <c r="W28" s="18">
-        <v>0</v>
-      </c>
-      <c r="X28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="18">
+        <v>7</v>
+      </c>
+      <c r="D28" s="19">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19">
+        <v>0</v>
+      </c>
+      <c r="F28" s="19">
+        <v>0</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0</v>
+      </c>
+      <c r="L28" s="19">
+        <v>0</v>
+      </c>
+      <c r="M28" s="19">
+        <v>0</v>
+      </c>
+      <c r="N28" s="19">
+        <v>0</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="19">
+        <v>0</v>
+      </c>
+      <c r="R28" s="19">
+        <v>0</v>
+      </c>
+      <c r="S28" s="19">
+        <v>0</v>
+      </c>
+      <c r="T28" s="19">
+        <v>0</v>
+      </c>
+      <c r="U28" s="19">
+        <v>0</v>
+      </c>
+      <c r="V28" s="19">
+        <v>0</v>
+      </c>
+      <c r="W28" s="19">
+        <v>0</v>
+      </c>
+      <c r="X28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
-        <v>15</v>
+      <c r="A29" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D29" s="19">
         <v>0</v>
@@ -4731,7 +4727,7 @@
     </row>
     <row r="30" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>3</v>
@@ -4865,13 +4861,13 @@
     </row>
     <row r="31" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31" s="19">
         <v>0</v>
@@ -4999,13 +4995,13 @@
     </row>
     <row r="32" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" s="19">
         <v>0</v>
@@ -5132,10 +5128,10 @@
       </c>
     </row>
     <row r="33" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="A33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -5267,13 +5263,13 @@
     </row>
     <row r="34" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="D34" s="19">
         <v>0</v>
@@ -5400,14 +5396,14 @@
       </c>
     </row>
     <row r="35" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="11" t="s">
+      <c r="A35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35" s="19">
         <v>0</v>
@@ -5535,13 +5531,13 @@
     </row>
     <row r="36" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36" s="19">
         <v>0</v>
@@ -5669,275 +5665,275 @@
     </row>
     <row r="37" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="19">
-        <v>0</v>
-      </c>
-      <c r="E37" s="19">
-        <v>0</v>
-      </c>
-      <c r="F37" s="19">
-        <v>0</v>
-      </c>
-      <c r="G37" s="19">
-        <v>0</v>
-      </c>
-      <c r="H37" s="19">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19">
-        <v>0</v>
-      </c>
-      <c r="L37" s="19">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0</v>
-      </c>
-      <c r="P37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="19">
-        <v>0</v>
-      </c>
-      <c r="R37" s="19">
-        <v>0</v>
-      </c>
-      <c r="S37" s="19">
-        <v>0</v>
-      </c>
-      <c r="T37" s="19">
-        <v>0</v>
-      </c>
-      <c r="U37" s="19">
-        <v>0</v>
-      </c>
-      <c r="V37" s="19">
-        <v>0</v>
-      </c>
-      <c r="W37" s="19">
-        <v>0</v>
-      </c>
-      <c r="X37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="19">
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="18">
+        <v>0</v>
+      </c>
+      <c r="E37" s="18">
+        <v>0</v>
+      </c>
+      <c r="F37" s="18">
+        <v>0</v>
+      </c>
+      <c r="G37" s="18">
+        <v>0</v>
+      </c>
+      <c r="H37" s="18">
+        <v>0</v>
+      </c>
+      <c r="I37" s="18">
+        <v>0</v>
+      </c>
+      <c r="J37" s="18">
+        <v>0</v>
+      </c>
+      <c r="K37" s="18">
+        <v>0</v>
+      </c>
+      <c r="L37" s="18">
+        <v>0</v>
+      </c>
+      <c r="M37" s="18">
+        <v>0</v>
+      </c>
+      <c r="N37" s="18">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18">
+        <v>0</v>
+      </c>
+      <c r="P37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>0</v>
+      </c>
+      <c r="R37" s="18">
+        <v>0</v>
+      </c>
+      <c r="S37" s="18">
+        <v>0</v>
+      </c>
+      <c r="T37" s="18">
+        <v>0</v>
+      </c>
+      <c r="U37" s="18">
+        <v>0</v>
+      </c>
+      <c r="V37" s="18">
+        <v>0</v>
+      </c>
+      <c r="W37" s="18">
+        <v>0</v>
+      </c>
+      <c r="X37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>3</v>
+      <c r="A38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19">
-        <v>0</v>
-      </c>
-      <c r="E38" s="19">
-        <v>0</v>
-      </c>
-      <c r="F38" s="19">
-        <v>0</v>
-      </c>
-      <c r="G38" s="19">
-        <v>0</v>
-      </c>
-      <c r="H38" s="19">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="19">
-        <v>0</v>
-      </c>
-      <c r="R38" s="19">
-        <v>0</v>
-      </c>
-      <c r="S38" s="19">
-        <v>0</v>
-      </c>
-      <c r="T38" s="19">
-        <v>0</v>
-      </c>
-      <c r="U38" s="19">
-        <v>0</v>
-      </c>
-      <c r="V38" s="19">
-        <v>0</v>
-      </c>
-      <c r="W38" s="19">
-        <v>0</v>
-      </c>
-      <c r="X38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="19">
+        <v>7</v>
+      </c>
+      <c r="D38" s="18">
+        <v>0</v>
+      </c>
+      <c r="E38" s="18">
+        <v>0</v>
+      </c>
+      <c r="F38" s="18">
+        <v>0</v>
+      </c>
+      <c r="G38" s="18">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>0</v>
+      </c>
+      <c r="I38" s="18">
+        <v>0</v>
+      </c>
+      <c r="J38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="18">
+        <v>0</v>
+      </c>
+      <c r="L38" s="18">
+        <v>0</v>
+      </c>
+      <c r="M38" s="18">
+        <v>0</v>
+      </c>
+      <c r="N38" s="18">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18">
+        <v>0</v>
+      </c>
+      <c r="P38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>0</v>
+      </c>
+      <c r="R38" s="18">
+        <v>0</v>
+      </c>
+      <c r="S38" s="18">
+        <v>0</v>
+      </c>
+      <c r="T38" s="18">
+        <v>0</v>
+      </c>
+      <c r="U38" s="18">
+        <v>0</v>
+      </c>
+      <c r="V38" s="18">
+        <v>0</v>
+      </c>
+      <c r="W38" s="18">
+        <v>0</v>
+      </c>
+      <c r="X38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>10</v>
@@ -5945,127 +5941,127 @@
       <c r="C39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="19">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19">
-        <v>0</v>
-      </c>
-      <c r="F39" s="19">
-        <v>0</v>
-      </c>
-      <c r="G39" s="19">
-        <v>0</v>
-      </c>
-      <c r="H39" s="19">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19">
-        <v>0</v>
-      </c>
-      <c r="L39" s="19">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19">
-        <v>0</v>
-      </c>
-      <c r="R39" s="19">
-        <v>0</v>
-      </c>
-      <c r="S39" s="19">
-        <v>0</v>
-      </c>
-      <c r="T39" s="19">
-        <v>0</v>
-      </c>
-      <c r="U39" s="19">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19">
-        <v>0</v>
-      </c>
-      <c r="W39" s="19">
-        <v>0</v>
-      </c>
-      <c r="X39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="19">
+      <c r="D39" s="18">
+        <v>0</v>
+      </c>
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+      <c r="F39" s="18">
+        <v>0</v>
+      </c>
+      <c r="G39" s="18">
+        <v>0</v>
+      </c>
+      <c r="H39" s="18">
+        <v>0</v>
+      </c>
+      <c r="I39" s="18">
+        <v>0</v>
+      </c>
+      <c r="J39" s="18">
+        <v>0</v>
+      </c>
+      <c r="K39" s="18">
+        <v>0</v>
+      </c>
+      <c r="L39" s="18">
+        <v>0</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0</v>
+      </c>
+      <c r="N39" s="18">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18">
+        <v>0</v>
+      </c>
+      <c r="P39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="18">
+        <v>0</v>
+      </c>
+      <c r="R39" s="18">
+        <v>0</v>
+      </c>
+      <c r="S39" s="18">
+        <v>0</v>
+      </c>
+      <c r="T39" s="18">
+        <v>0</v>
+      </c>
+      <c r="U39" s="18">
+        <v>0</v>
+      </c>
+      <c r="V39" s="18">
+        <v>0</v>
+      </c>
+      <c r="W39" s="18">
+        <v>0</v>
+      </c>
+      <c r="X39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="18">
         <v>0</v>
       </c>
     </row>
@@ -15993,7 +15989,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4224F1-5D48-4FE4-980F-718DB45087F0}">
   <dimension ref="A1:AR113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.08984375" customWidth="1"/>
     <col min="2" max="2" width="13.7265625" customWidth="1"/>
@@ -17475,7 +17471,7 @@
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>3</v>
@@ -17609,7 +17605,7 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>6</v>
@@ -17743,7 +17739,7 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>10</v>
@@ -17877,7 +17873,7 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>3</v>
@@ -18011,7 +18007,7 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>6</v>
@@ -18145,7 +18141,7 @@
     </row>
     <row r="17" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>10</v>
@@ -18279,7 +18275,7 @@
     </row>
     <row r="18" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>3</v>
@@ -18413,7 +18409,7 @@
     </row>
     <row r="19" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>6</v>
@@ -18547,7 +18543,7 @@
     </row>
     <row r="20" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>10</v>
@@ -18680,10 +18676,10 @@
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -18814,14 +18810,14 @@
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>6</v>
+      <c r="A22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D22" s="18">
         <v>0</v>
@@ -18948,8 +18944,8 @@
       </c>
     </row>
     <row r="23" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>13</v>
+      <c r="A23" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>10</v>
@@ -19082,14 +19078,14 @@
       </c>
     </row>
     <row r="24" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>3</v>
+      <c r="A24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" s="18">
         <v>0</v>
@@ -19217,7 +19213,7 @@
     </row>
     <row r="25" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>3</v>
@@ -19351,7 +19347,7 @@
     </row>
     <row r="26" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>10</v>
@@ -19359,407 +19355,407 @@
       <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="18">
-        <v>0</v>
-      </c>
-      <c r="E26" s="18">
-        <v>0</v>
-      </c>
-      <c r="F26" s="18">
-        <v>0</v>
-      </c>
-      <c r="G26" s="18">
-        <v>0</v>
-      </c>
-      <c r="H26" s="18">
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="18">
-        <v>0</v>
-      </c>
-      <c r="K26" s="18">
-        <v>0</v>
-      </c>
-      <c r="L26" s="18">
-        <v>0</v>
-      </c>
-      <c r="M26" s="18">
-        <v>0</v>
-      </c>
-      <c r="N26" s="18">
-        <v>0</v>
-      </c>
-      <c r="O26" s="18">
-        <v>0</v>
-      </c>
-      <c r="P26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="18">
-        <v>0</v>
-      </c>
-      <c r="R26" s="18">
-        <v>0</v>
-      </c>
-      <c r="S26" s="18">
-        <v>0</v>
-      </c>
-      <c r="T26" s="18">
-        <v>0</v>
-      </c>
-      <c r="U26" s="18">
-        <v>0</v>
-      </c>
-      <c r="V26" s="18">
-        <v>0</v>
-      </c>
-      <c r="W26" s="18">
-        <v>0</v>
-      </c>
-      <c r="X26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="18">
+      <c r="D26" s="19">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
+        <v>0</v>
+      </c>
+      <c r="O26" s="19">
+        <v>0</v>
+      </c>
+      <c r="P26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="19">
+        <v>0</v>
+      </c>
+      <c r="R26" s="19">
+        <v>0</v>
+      </c>
+      <c r="S26" s="19">
+        <v>0</v>
+      </c>
+      <c r="T26" s="19">
+        <v>0</v>
+      </c>
+      <c r="U26" s="19">
+        <v>0</v>
+      </c>
+      <c r="V26" s="19">
+        <v>0</v>
+      </c>
+      <c r="W26" s="19">
+        <v>0</v>
+      </c>
+      <c r="X26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR26" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>10</v>
+      <c r="A27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0</v>
-      </c>
-      <c r="E27" s="18">
-        <v>0</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-      <c r="G27" s="18">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <v>0</v>
-      </c>
-      <c r="J27" s="18">
-        <v>0</v>
-      </c>
-      <c r="K27" s="18">
-        <v>0</v>
-      </c>
-      <c r="L27" s="18">
-        <v>0</v>
-      </c>
-      <c r="M27" s="18">
-        <v>0</v>
-      </c>
-      <c r="N27" s="18">
-        <v>0</v>
-      </c>
-      <c r="O27" s="18">
-        <v>0</v>
-      </c>
-      <c r="P27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
-        <v>0</v>
-      </c>
-      <c r="S27" s="18">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18">
-        <v>0</v>
-      </c>
-      <c r="U27" s="18">
-        <v>0</v>
-      </c>
-      <c r="V27" s="18">
-        <v>0</v>
-      </c>
-      <c r="W27" s="18">
-        <v>0</v>
-      </c>
-      <c r="X27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="18">
+        <v>1</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19">
+        <v>0</v>
+      </c>
+      <c r="P27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>0</v>
+      </c>
+      <c r="R27" s="19">
+        <v>0</v>
+      </c>
+      <c r="S27" s="19">
+        <v>0</v>
+      </c>
+      <c r="T27" s="19">
+        <v>0</v>
+      </c>
+      <c r="U27" s="19">
+        <v>0</v>
+      </c>
+      <c r="V27" s="19">
+        <v>0</v>
+      </c>
+      <c r="W27" s="19">
+        <v>0</v>
+      </c>
+      <c r="X27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>15</v>
+      <c r="A28" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18">
-        <v>0</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-      <c r="G28" s="18">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18">
-        <v>0</v>
-      </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="18">
-        <v>0</v>
-      </c>
-      <c r="K28" s="18">
-        <v>0</v>
-      </c>
-      <c r="L28" s="18">
-        <v>0</v>
-      </c>
-      <c r="M28" s="18">
-        <v>0</v>
-      </c>
-      <c r="N28" s="18">
-        <v>0</v>
-      </c>
-      <c r="O28" s="18">
-        <v>0</v>
-      </c>
-      <c r="P28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>0</v>
-      </c>
-      <c r="R28" s="18">
-        <v>0</v>
-      </c>
-      <c r="S28" s="18">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18">
-        <v>0</v>
-      </c>
-      <c r="U28" s="18">
-        <v>0</v>
-      </c>
-      <c r="V28" s="18">
-        <v>0</v>
-      </c>
-      <c r="W28" s="18">
-        <v>0</v>
-      </c>
-      <c r="X28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="18">
+        <v>7</v>
+      </c>
+      <c r="D28" s="19">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19">
+        <v>0</v>
+      </c>
+      <c r="F28" s="19">
+        <v>0</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0</v>
+      </c>
+      <c r="L28" s="19">
+        <v>0</v>
+      </c>
+      <c r="M28" s="19">
+        <v>0</v>
+      </c>
+      <c r="N28" s="19">
+        <v>0</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="19">
+        <v>0</v>
+      </c>
+      <c r="R28" s="19">
+        <v>0</v>
+      </c>
+      <c r="S28" s="19">
+        <v>0</v>
+      </c>
+      <c r="T28" s="19">
+        <v>0</v>
+      </c>
+      <c r="U28" s="19">
+        <v>0</v>
+      </c>
+      <c r="V28" s="19">
+        <v>0</v>
+      </c>
+      <c r="W28" s="19">
+        <v>0</v>
+      </c>
+      <c r="X28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
-        <v>15</v>
+      <c r="A29" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D29" s="19">
         <v>0</v>
@@ -19887,7 +19883,7 @@
     </row>
     <row r="30" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>3</v>
@@ -20021,13 +20017,13 @@
     </row>
     <row r="31" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31" s="19">
         <v>0</v>
@@ -20155,13 +20151,13 @@
     </row>
     <row r="32" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" s="19">
         <v>0</v>
@@ -20288,10 +20284,10 @@
       </c>
     </row>
     <row r="33" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="A33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -20423,13 +20419,13 @@
     </row>
     <row r="34" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="D34" s="19">
         <v>0</v>
@@ -20556,14 +20552,14 @@
       </c>
     </row>
     <row r="35" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="11" t="s">
+      <c r="A35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35" s="19">
         <v>0</v>
@@ -20691,13 +20687,13 @@
     </row>
     <row r="36" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36" s="19">
         <v>0</v>
@@ -20825,275 +20821,275 @@
     </row>
     <row r="37" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="19">
-        <v>0</v>
-      </c>
-      <c r="E37" s="19">
-        <v>0</v>
-      </c>
-      <c r="F37" s="19">
-        <v>0</v>
-      </c>
-      <c r="G37" s="19">
-        <v>0</v>
-      </c>
-      <c r="H37" s="19">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19">
-        <v>0</v>
-      </c>
-      <c r="L37" s="19">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0</v>
-      </c>
-      <c r="P37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="19">
-        <v>0</v>
-      </c>
-      <c r="R37" s="19">
-        <v>0</v>
-      </c>
-      <c r="S37" s="19">
-        <v>0</v>
-      </c>
-      <c r="T37" s="19">
-        <v>0</v>
-      </c>
-      <c r="U37" s="19">
-        <v>0</v>
-      </c>
-      <c r="V37" s="19">
-        <v>0</v>
-      </c>
-      <c r="W37" s="19">
-        <v>0</v>
-      </c>
-      <c r="X37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="19">
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="18">
+        <v>0</v>
+      </c>
+      <c r="E37" s="18">
+        <v>0</v>
+      </c>
+      <c r="F37" s="18">
+        <v>0</v>
+      </c>
+      <c r="G37" s="18">
+        <v>0</v>
+      </c>
+      <c r="H37" s="18">
+        <v>0</v>
+      </c>
+      <c r="I37" s="18">
+        <v>0</v>
+      </c>
+      <c r="J37" s="18">
+        <v>0</v>
+      </c>
+      <c r="K37" s="18">
+        <v>0</v>
+      </c>
+      <c r="L37" s="18">
+        <v>0</v>
+      </c>
+      <c r="M37" s="18">
+        <v>0</v>
+      </c>
+      <c r="N37" s="18">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18">
+        <v>0</v>
+      </c>
+      <c r="P37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>0</v>
+      </c>
+      <c r="R37" s="18">
+        <v>0</v>
+      </c>
+      <c r="S37" s="18">
+        <v>0</v>
+      </c>
+      <c r="T37" s="18">
+        <v>0</v>
+      </c>
+      <c r="U37" s="18">
+        <v>0</v>
+      </c>
+      <c r="V37" s="18">
+        <v>0</v>
+      </c>
+      <c r="W37" s="18">
+        <v>0</v>
+      </c>
+      <c r="X37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>3</v>
+      <c r="A38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19">
-        <v>0</v>
-      </c>
-      <c r="E38" s="19">
-        <v>0</v>
-      </c>
-      <c r="F38" s="19">
-        <v>0</v>
-      </c>
-      <c r="G38" s="19">
-        <v>0</v>
-      </c>
-      <c r="H38" s="19">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="19">
-        <v>0</v>
-      </c>
-      <c r="R38" s="19">
-        <v>0</v>
-      </c>
-      <c r="S38" s="19">
-        <v>0</v>
-      </c>
-      <c r="T38" s="19">
-        <v>0</v>
-      </c>
-      <c r="U38" s="19">
-        <v>0</v>
-      </c>
-      <c r="V38" s="19">
-        <v>0</v>
-      </c>
-      <c r="W38" s="19">
-        <v>0</v>
-      </c>
-      <c r="X38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="19">
+        <v>7</v>
+      </c>
+      <c r="D38" s="18">
+        <v>0</v>
+      </c>
+      <c r="E38" s="18">
+        <v>0</v>
+      </c>
+      <c r="F38" s="18">
+        <v>0</v>
+      </c>
+      <c r="G38" s="18">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>0</v>
+      </c>
+      <c r="I38" s="18">
+        <v>0</v>
+      </c>
+      <c r="J38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="18">
+        <v>0</v>
+      </c>
+      <c r="L38" s="18">
+        <v>0</v>
+      </c>
+      <c r="M38" s="18">
+        <v>0</v>
+      </c>
+      <c r="N38" s="18">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18">
+        <v>0</v>
+      </c>
+      <c r="P38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>0</v>
+      </c>
+      <c r="R38" s="18">
+        <v>0</v>
+      </c>
+      <c r="S38" s="18">
+        <v>0</v>
+      </c>
+      <c r="T38" s="18">
+        <v>0</v>
+      </c>
+      <c r="U38" s="18">
+        <v>0</v>
+      </c>
+      <c r="V38" s="18">
+        <v>0</v>
+      </c>
+      <c r="W38" s="18">
+        <v>0</v>
+      </c>
+      <c r="X38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>10</v>
@@ -21101,127 +21097,127 @@
       <c r="C39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="19">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19">
-        <v>0</v>
-      </c>
-      <c r="F39" s="19">
-        <v>0</v>
-      </c>
-      <c r="G39" s="19">
-        <v>0</v>
-      </c>
-      <c r="H39" s="19">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19">
-        <v>0</v>
-      </c>
-      <c r="L39" s="19">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19">
-        <v>0</v>
-      </c>
-      <c r="R39" s="19">
-        <v>0</v>
-      </c>
-      <c r="S39" s="19">
-        <v>0</v>
-      </c>
-      <c r="T39" s="19">
-        <v>0</v>
-      </c>
-      <c r="U39" s="19">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19">
-        <v>0</v>
-      </c>
-      <c r="W39" s="19">
-        <v>0</v>
-      </c>
-      <c r="X39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="19">
+      <c r="D39" s="18">
+        <v>0</v>
+      </c>
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+      <c r="F39" s="18">
+        <v>0</v>
+      </c>
+      <c r="G39" s="18">
+        <v>0</v>
+      </c>
+      <c r="H39" s="18">
+        <v>0</v>
+      </c>
+      <c r="I39" s="18">
+        <v>0</v>
+      </c>
+      <c r="J39" s="18">
+        <v>0</v>
+      </c>
+      <c r="K39" s="18">
+        <v>0</v>
+      </c>
+      <c r="L39" s="18">
+        <v>0</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0</v>
+      </c>
+      <c r="N39" s="18">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18">
+        <v>0</v>
+      </c>
+      <c r="P39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="18">
+        <v>0</v>
+      </c>
+      <c r="R39" s="18">
+        <v>0</v>
+      </c>
+      <c r="S39" s="18">
+        <v>0</v>
+      </c>
+      <c r="T39" s="18">
+        <v>0</v>
+      </c>
+      <c r="U39" s="18">
+        <v>0</v>
+      </c>
+      <c r="V39" s="18">
+        <v>0</v>
+      </c>
+      <c r="W39" s="18">
+        <v>0</v>
+      </c>
+      <c r="X39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="18">
         <v>0</v>
       </c>
     </row>
@@ -31149,7 +31145,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{410D20C9-BA4A-4E8A-B726-CB9469D468A2}">
   <dimension ref="A1:AR113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="13.6328125" customWidth="1"/>
@@ -32631,7 +32627,7 @@
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>3</v>
@@ -32765,7 +32761,7 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>6</v>
@@ -32899,7 +32895,7 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>10</v>
@@ -33033,7 +33029,7 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>3</v>
@@ -33167,7 +33163,7 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>6</v>
@@ -33301,7 +33297,7 @@
     </row>
     <row r="17" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>10</v>
@@ -33435,7 +33431,7 @@
     </row>
     <row r="18" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>3</v>
@@ -33569,7 +33565,7 @@
     </row>
     <row r="19" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>6</v>
@@ -33703,7 +33699,7 @@
     </row>
     <row r="20" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>10</v>
@@ -33836,10 +33832,10 @@
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -33970,14 +33966,14 @@
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>6</v>
+      <c r="A22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D22" s="18">
         <v>0</v>
@@ -34104,8 +34100,8 @@
       </c>
     </row>
     <row r="23" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>13</v>
+      <c r="A23" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>10</v>
@@ -34238,14 +34234,14 @@
       </c>
     </row>
     <row r="24" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>3</v>
+      <c r="A24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" s="18">
         <v>0</v>
@@ -34373,7 +34369,7 @@
     </row>
     <row r="25" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>3</v>
@@ -34507,7 +34503,7 @@
     </row>
     <row r="26" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>10</v>
@@ -34515,407 +34511,407 @@
       <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="18">
-        <v>0</v>
-      </c>
-      <c r="E26" s="18">
-        <v>0</v>
-      </c>
-      <c r="F26" s="18">
-        <v>0</v>
-      </c>
-      <c r="G26" s="18">
-        <v>0</v>
-      </c>
-      <c r="H26" s="18">
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="18">
-        <v>0</v>
-      </c>
-      <c r="K26" s="18">
-        <v>0</v>
-      </c>
-      <c r="L26" s="18">
-        <v>0</v>
-      </c>
-      <c r="M26" s="18">
-        <v>0</v>
-      </c>
-      <c r="N26" s="18">
-        <v>0</v>
-      </c>
-      <c r="O26" s="18">
-        <v>0</v>
-      </c>
-      <c r="P26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="18">
-        <v>0</v>
-      </c>
-      <c r="R26" s="18">
-        <v>0</v>
-      </c>
-      <c r="S26" s="18">
-        <v>0</v>
-      </c>
-      <c r="T26" s="18">
-        <v>0</v>
-      </c>
-      <c r="U26" s="18">
-        <v>0</v>
-      </c>
-      <c r="V26" s="18">
-        <v>0</v>
-      </c>
-      <c r="W26" s="18">
-        <v>0</v>
-      </c>
-      <c r="X26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="18">
+      <c r="D26" s="19">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
+        <v>0</v>
+      </c>
+      <c r="O26" s="19">
+        <v>0</v>
+      </c>
+      <c r="P26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="19">
+        <v>0</v>
+      </c>
+      <c r="R26" s="19">
+        <v>0</v>
+      </c>
+      <c r="S26" s="19">
+        <v>0</v>
+      </c>
+      <c r="T26" s="19">
+        <v>0</v>
+      </c>
+      <c r="U26" s="19">
+        <v>0</v>
+      </c>
+      <c r="V26" s="19">
+        <v>0</v>
+      </c>
+      <c r="W26" s="19">
+        <v>0</v>
+      </c>
+      <c r="X26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR26" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>10</v>
+      <c r="A27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0</v>
-      </c>
-      <c r="E27" s="18">
-        <v>0</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-      <c r="G27" s="18">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <v>0</v>
-      </c>
-      <c r="J27" s="18">
-        <v>0</v>
-      </c>
-      <c r="K27" s="18">
-        <v>0</v>
-      </c>
-      <c r="L27" s="18">
-        <v>0</v>
-      </c>
-      <c r="M27" s="18">
-        <v>0</v>
-      </c>
-      <c r="N27" s="18">
-        <v>0</v>
-      </c>
-      <c r="O27" s="18">
-        <v>0</v>
-      </c>
-      <c r="P27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
-        <v>0</v>
-      </c>
-      <c r="S27" s="18">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18">
-        <v>0</v>
-      </c>
-      <c r="U27" s="18">
-        <v>0</v>
-      </c>
-      <c r="V27" s="18">
-        <v>0</v>
-      </c>
-      <c r="W27" s="18">
-        <v>0</v>
-      </c>
-      <c r="X27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="18">
+        <v>1</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19">
+        <v>0</v>
+      </c>
+      <c r="P27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>0</v>
+      </c>
+      <c r="R27" s="19">
+        <v>0</v>
+      </c>
+      <c r="S27" s="19">
+        <v>0</v>
+      </c>
+      <c r="T27" s="19">
+        <v>0</v>
+      </c>
+      <c r="U27" s="19">
+        <v>0</v>
+      </c>
+      <c r="V27" s="19">
+        <v>0</v>
+      </c>
+      <c r="W27" s="19">
+        <v>0</v>
+      </c>
+      <c r="X27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>15</v>
+      <c r="A28" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18">
-        <v>0</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-      <c r="G28" s="18">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18">
-        <v>0</v>
-      </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="18">
-        <v>0</v>
-      </c>
-      <c r="K28" s="18">
-        <v>0</v>
-      </c>
-      <c r="L28" s="18">
-        <v>0</v>
-      </c>
-      <c r="M28" s="18">
-        <v>0</v>
-      </c>
-      <c r="N28" s="18">
-        <v>0</v>
-      </c>
-      <c r="O28" s="18">
-        <v>0</v>
-      </c>
-      <c r="P28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>0</v>
-      </c>
-      <c r="R28" s="18">
-        <v>0</v>
-      </c>
-      <c r="S28" s="18">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18">
-        <v>0</v>
-      </c>
-      <c r="U28" s="18">
-        <v>0</v>
-      </c>
-      <c r="V28" s="18">
-        <v>0</v>
-      </c>
-      <c r="W28" s="18">
-        <v>0</v>
-      </c>
-      <c r="X28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="18">
+        <v>7</v>
+      </c>
+      <c r="D28" s="19">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19">
+        <v>0</v>
+      </c>
+      <c r="F28" s="19">
+        <v>0</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0</v>
+      </c>
+      <c r="L28" s="19">
+        <v>0</v>
+      </c>
+      <c r="M28" s="19">
+        <v>0</v>
+      </c>
+      <c r="N28" s="19">
+        <v>0</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="19">
+        <v>0</v>
+      </c>
+      <c r="R28" s="19">
+        <v>0</v>
+      </c>
+      <c r="S28" s="19">
+        <v>0</v>
+      </c>
+      <c r="T28" s="19">
+        <v>0</v>
+      </c>
+      <c r="U28" s="19">
+        <v>0</v>
+      </c>
+      <c r="V28" s="19">
+        <v>0</v>
+      </c>
+      <c r="W28" s="19">
+        <v>0</v>
+      </c>
+      <c r="X28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
-        <v>15</v>
+      <c r="A29" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D29" s="19">
         <v>0</v>
@@ -35043,7 +35039,7 @@
     </row>
     <row r="30" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>3</v>
@@ -35177,13 +35173,13 @@
     </row>
     <row r="31" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31" s="19">
         <v>0</v>
@@ -35311,13 +35307,13 @@
     </row>
     <row r="32" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" s="19">
         <v>0</v>
@@ -35444,10 +35440,10 @@
       </c>
     </row>
     <row r="33" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="A33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -35579,13 +35575,13 @@
     </row>
     <row r="34" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="D34" s="19">
         <v>0</v>
@@ -35712,14 +35708,14 @@
       </c>
     </row>
     <row r="35" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="11" t="s">
+      <c r="A35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35" s="19">
         <v>0</v>
@@ -35847,13 +35843,13 @@
     </row>
     <row r="36" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36" s="19">
         <v>0</v>
@@ -35981,275 +35977,275 @@
     </row>
     <row r="37" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="19">
-        <v>0</v>
-      </c>
-      <c r="E37" s="19">
-        <v>0</v>
-      </c>
-      <c r="F37" s="19">
-        <v>0</v>
-      </c>
-      <c r="G37" s="19">
-        <v>0</v>
-      </c>
-      <c r="H37" s="19">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19">
-        <v>0</v>
-      </c>
-      <c r="L37" s="19">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0</v>
-      </c>
-      <c r="P37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="19">
-        <v>0</v>
-      </c>
-      <c r="R37" s="19">
-        <v>0</v>
-      </c>
-      <c r="S37" s="19">
-        <v>0</v>
-      </c>
-      <c r="T37" s="19">
-        <v>0</v>
-      </c>
-      <c r="U37" s="19">
-        <v>0</v>
-      </c>
-      <c r="V37" s="19">
-        <v>0</v>
-      </c>
-      <c r="W37" s="19">
-        <v>0</v>
-      </c>
-      <c r="X37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="19">
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="18">
+        <v>0</v>
+      </c>
+      <c r="E37" s="18">
+        <v>0</v>
+      </c>
+      <c r="F37" s="18">
+        <v>0</v>
+      </c>
+      <c r="G37" s="18">
+        <v>0</v>
+      </c>
+      <c r="H37" s="18">
+        <v>0</v>
+      </c>
+      <c r="I37" s="18">
+        <v>0</v>
+      </c>
+      <c r="J37" s="18">
+        <v>0</v>
+      </c>
+      <c r="K37" s="18">
+        <v>0</v>
+      </c>
+      <c r="L37" s="18">
+        <v>0</v>
+      </c>
+      <c r="M37" s="18">
+        <v>0</v>
+      </c>
+      <c r="N37" s="18">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18">
+        <v>0</v>
+      </c>
+      <c r="P37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>0</v>
+      </c>
+      <c r="R37" s="18">
+        <v>0</v>
+      </c>
+      <c r="S37" s="18">
+        <v>0</v>
+      </c>
+      <c r="T37" s="18">
+        <v>0</v>
+      </c>
+      <c r="U37" s="18">
+        <v>0</v>
+      </c>
+      <c r="V37" s="18">
+        <v>0</v>
+      </c>
+      <c r="W37" s="18">
+        <v>0</v>
+      </c>
+      <c r="X37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>3</v>
+      <c r="A38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19">
-        <v>0</v>
-      </c>
-      <c r="E38" s="19">
-        <v>0</v>
-      </c>
-      <c r="F38" s="19">
-        <v>0</v>
-      </c>
-      <c r="G38" s="19">
-        <v>0</v>
-      </c>
-      <c r="H38" s="19">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="19">
-        <v>0</v>
-      </c>
-      <c r="R38" s="19">
-        <v>0</v>
-      </c>
-      <c r="S38" s="19">
-        <v>0</v>
-      </c>
-      <c r="T38" s="19">
-        <v>0</v>
-      </c>
-      <c r="U38" s="19">
-        <v>0</v>
-      </c>
-      <c r="V38" s="19">
-        <v>0</v>
-      </c>
-      <c r="W38" s="19">
-        <v>0</v>
-      </c>
-      <c r="X38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="19">
+        <v>7</v>
+      </c>
+      <c r="D38" s="18">
+        <v>0</v>
+      </c>
+      <c r="E38" s="18">
+        <v>0</v>
+      </c>
+      <c r="F38" s="18">
+        <v>0</v>
+      </c>
+      <c r="G38" s="18">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>0</v>
+      </c>
+      <c r="I38" s="18">
+        <v>0</v>
+      </c>
+      <c r="J38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="18">
+        <v>0</v>
+      </c>
+      <c r="L38" s="18">
+        <v>0</v>
+      </c>
+      <c r="M38" s="18">
+        <v>0</v>
+      </c>
+      <c r="N38" s="18">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18">
+        <v>0</v>
+      </c>
+      <c r="P38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>0</v>
+      </c>
+      <c r="R38" s="18">
+        <v>0</v>
+      </c>
+      <c r="S38" s="18">
+        <v>0</v>
+      </c>
+      <c r="T38" s="18">
+        <v>0</v>
+      </c>
+      <c r="U38" s="18">
+        <v>0</v>
+      </c>
+      <c r="V38" s="18">
+        <v>0</v>
+      </c>
+      <c r="W38" s="18">
+        <v>0</v>
+      </c>
+      <c r="X38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>10</v>
@@ -36257,127 +36253,127 @@
       <c r="C39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="19">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19">
-        <v>0</v>
-      </c>
-      <c r="F39" s="19">
-        <v>0</v>
-      </c>
-      <c r="G39" s="19">
-        <v>0</v>
-      </c>
-      <c r="H39" s="19">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19">
-        <v>0</v>
-      </c>
-      <c r="L39" s="19">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19">
-        <v>0</v>
-      </c>
-      <c r="R39" s="19">
-        <v>0</v>
-      </c>
-      <c r="S39" s="19">
-        <v>0</v>
-      </c>
-      <c r="T39" s="19">
-        <v>0</v>
-      </c>
-      <c r="U39" s="19">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19">
-        <v>0</v>
-      </c>
-      <c r="W39" s="19">
-        <v>0</v>
-      </c>
-      <c r="X39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="19">
+      <c r="D39" s="18">
+        <v>0</v>
+      </c>
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+      <c r="F39" s="18">
+        <v>0</v>
+      </c>
+      <c r="G39" s="18">
+        <v>0</v>
+      </c>
+      <c r="H39" s="18">
+        <v>0</v>
+      </c>
+      <c r="I39" s="18">
+        <v>0</v>
+      </c>
+      <c r="J39" s="18">
+        <v>0</v>
+      </c>
+      <c r="K39" s="18">
+        <v>0</v>
+      </c>
+      <c r="L39" s="18">
+        <v>0</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0</v>
+      </c>
+      <c r="N39" s="18">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18">
+        <v>0</v>
+      </c>
+      <c r="P39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="18">
+        <v>0</v>
+      </c>
+      <c r="R39" s="18">
+        <v>0</v>
+      </c>
+      <c r="S39" s="18">
+        <v>0</v>
+      </c>
+      <c r="T39" s="18">
+        <v>0</v>
+      </c>
+      <c r="U39" s="18">
+        <v>0</v>
+      </c>
+      <c r="V39" s="18">
+        <v>0</v>
+      </c>
+      <c r="W39" s="18">
+        <v>0</v>
+      </c>
+      <c r="X39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="18">
         <v>0</v>
       </c>
     </row>
@@ -46306,7 +46302,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AR113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" customWidth="1"/>
     <col min="2" max="2" width="13.26953125" customWidth="1"/>
@@ -47788,7 +47784,7 @@
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>3</v>
@@ -47922,7 +47918,7 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>6</v>
@@ -48056,7 +48052,7 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>10</v>
@@ -48190,7 +48186,7 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>3</v>
@@ -48324,7 +48320,7 @@
     </row>
     <row r="16" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>6</v>
@@ -48458,7 +48454,7 @@
     </row>
     <row r="17" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>10</v>
@@ -48592,7 +48588,7 @@
     </row>
     <row r="18" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>3</v>
@@ -48726,7 +48722,7 @@
     </row>
     <row r="19" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>6</v>
@@ -48860,7 +48856,7 @@
     </row>
     <row r="20" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>10</v>
@@ -48993,10 +48989,10 @@
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -49127,14 +49123,14 @@
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>6</v>
+      <c r="A22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>3</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D22" s="18">
         <v>0</v>
@@ -49261,8 +49257,8 @@
       </c>
     </row>
     <row r="23" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>13</v>
+      <c r="A23" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>10</v>
@@ -49395,14 +49391,14 @@
       </c>
     </row>
     <row r="24" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>3</v>
+      <c r="A24" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" s="18">
         <v>0</v>
@@ -49530,7 +49526,7 @@
     </row>
     <row r="25" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>3</v>
@@ -49664,7 +49660,7 @@
     </row>
     <row r="26" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>10</v>
@@ -49672,407 +49668,407 @@
       <c r="C26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="18">
-        <v>0</v>
-      </c>
-      <c r="E26" s="18">
-        <v>0</v>
-      </c>
-      <c r="F26" s="18">
-        <v>0</v>
-      </c>
-      <c r="G26" s="18">
-        <v>0</v>
-      </c>
-      <c r="H26" s="18">
-        <v>0</v>
-      </c>
-      <c r="I26" s="18">
-        <v>0</v>
-      </c>
-      <c r="J26" s="18">
-        <v>0</v>
-      </c>
-      <c r="K26" s="18">
-        <v>0</v>
-      </c>
-      <c r="L26" s="18">
-        <v>0</v>
-      </c>
-      <c r="M26" s="18">
-        <v>0</v>
-      </c>
-      <c r="N26" s="18">
-        <v>0</v>
-      </c>
-      <c r="O26" s="18">
-        <v>0</v>
-      </c>
-      <c r="P26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="18">
-        <v>0</v>
-      </c>
-      <c r="R26" s="18">
-        <v>0</v>
-      </c>
-      <c r="S26" s="18">
-        <v>0</v>
-      </c>
-      <c r="T26" s="18">
-        <v>0</v>
-      </c>
-      <c r="U26" s="18">
-        <v>0</v>
-      </c>
-      <c r="V26" s="18">
-        <v>0</v>
-      </c>
-      <c r="W26" s="18">
-        <v>0</v>
-      </c>
-      <c r="X26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ26" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="18">
+      <c r="D26" s="19">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
+        <v>0</v>
+      </c>
+      <c r="O26" s="19">
+        <v>0</v>
+      </c>
+      <c r="P26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="19">
+        <v>0</v>
+      </c>
+      <c r="R26" s="19">
+        <v>0</v>
+      </c>
+      <c r="S26" s="19">
+        <v>0</v>
+      </c>
+      <c r="T26" s="19">
+        <v>0</v>
+      </c>
+      <c r="U26" s="19">
+        <v>0</v>
+      </c>
+      <c r="V26" s="19">
+        <v>0</v>
+      </c>
+      <c r="W26" s="19">
+        <v>0</v>
+      </c>
+      <c r="X26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR26" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>10</v>
+      <c r="A27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0</v>
-      </c>
-      <c r="E27" s="18">
-        <v>0</v>
-      </c>
-      <c r="F27" s="18">
-        <v>0</v>
-      </c>
-      <c r="G27" s="18">
-        <v>0</v>
-      </c>
-      <c r="H27" s="18">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <v>0</v>
-      </c>
-      <c r="J27" s="18">
-        <v>0</v>
-      </c>
-      <c r="K27" s="18">
-        <v>0</v>
-      </c>
-      <c r="L27" s="18">
-        <v>0</v>
-      </c>
-      <c r="M27" s="18">
-        <v>0</v>
-      </c>
-      <c r="N27" s="18">
-        <v>0</v>
-      </c>
-      <c r="O27" s="18">
-        <v>0</v>
-      </c>
-      <c r="P27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
-        <v>0</v>
-      </c>
-      <c r="S27" s="18">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18">
-        <v>0</v>
-      </c>
-      <c r="U27" s="18">
-        <v>0</v>
-      </c>
-      <c r="V27" s="18">
-        <v>0</v>
-      </c>
-      <c r="W27" s="18">
-        <v>0</v>
-      </c>
-      <c r="X27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ27" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="18">
+        <v>1</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19">
+        <v>0</v>
+      </c>
+      <c r="P27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>0</v>
+      </c>
+      <c r="R27" s="19">
+        <v>0</v>
+      </c>
+      <c r="S27" s="19">
+        <v>0</v>
+      </c>
+      <c r="T27" s="19">
+        <v>0</v>
+      </c>
+      <c r="U27" s="19">
+        <v>0</v>
+      </c>
+      <c r="V27" s="19">
+        <v>0</v>
+      </c>
+      <c r="W27" s="19">
+        <v>0</v>
+      </c>
+      <c r="X27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>15</v>
+      <c r="A28" s="11" t="s">
+        <v>16</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18">
-        <v>0</v>
-      </c>
-      <c r="F28" s="18">
-        <v>0</v>
-      </c>
-      <c r="G28" s="18">
-        <v>0</v>
-      </c>
-      <c r="H28" s="18">
-        <v>0</v>
-      </c>
-      <c r="I28" s="18">
-        <v>0</v>
-      </c>
-      <c r="J28" s="18">
-        <v>0</v>
-      </c>
-      <c r="K28" s="18">
-        <v>0</v>
-      </c>
-      <c r="L28" s="18">
-        <v>0</v>
-      </c>
-      <c r="M28" s="18">
-        <v>0</v>
-      </c>
-      <c r="N28" s="18">
-        <v>0</v>
-      </c>
-      <c r="O28" s="18">
-        <v>0</v>
-      </c>
-      <c r="P28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>0</v>
-      </c>
-      <c r="R28" s="18">
-        <v>0</v>
-      </c>
-      <c r="S28" s="18">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18">
-        <v>0</v>
-      </c>
-      <c r="U28" s="18">
-        <v>0</v>
-      </c>
-      <c r="V28" s="18">
-        <v>0</v>
-      </c>
-      <c r="W28" s="18">
-        <v>0</v>
-      </c>
-      <c r="X28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AD28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AE28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="18">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="18">
+        <v>7</v>
+      </c>
+      <c r="D28" s="19">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19">
+        <v>0</v>
+      </c>
+      <c r="F28" s="19">
+        <v>0</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0</v>
+      </c>
+      <c r="L28" s="19">
+        <v>0</v>
+      </c>
+      <c r="M28" s="19">
+        <v>0</v>
+      </c>
+      <c r="N28" s="19">
+        <v>0</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="19">
+        <v>0</v>
+      </c>
+      <c r="R28" s="19">
+        <v>0</v>
+      </c>
+      <c r="S28" s="19">
+        <v>0</v>
+      </c>
+      <c r="T28" s="19">
+        <v>0</v>
+      </c>
+      <c r="U28" s="19">
+        <v>0</v>
+      </c>
+      <c r="V28" s="19">
+        <v>0</v>
+      </c>
+      <c r="W28" s="19">
+        <v>0</v>
+      </c>
+      <c r="X28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="19">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="9" t="s">
-        <v>15</v>
+      <c r="A29" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D29" s="19">
         <v>0</v>
@@ -50200,7 +50196,7 @@
     </row>
     <row r="30" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>3</v>
@@ -50334,13 +50330,13 @@
     </row>
     <row r="31" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31" s="19">
         <v>0</v>
@@ -50468,13 +50464,13 @@
     </row>
     <row r="32" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" s="19">
         <v>0</v>
@@ -50601,10 +50597,10 @@
       </c>
     </row>
     <row r="33" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="A33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -50736,13 +50732,13 @@
     </row>
     <row r="34" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>1</v>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="D34" s="19">
         <v>0</v>
@@ -50869,14 +50865,14 @@
       </c>
     </row>
     <row r="35" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="11" t="s">
+      <c r="A35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D35" s="19">
         <v>0</v>
@@ -51004,13 +51000,13 @@
     </row>
     <row r="36" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36" s="19">
         <v>0</v>
@@ -51138,275 +51134,275 @@
     </row>
     <row r="37" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="19">
-        <v>0</v>
-      </c>
-      <c r="E37" s="19">
-        <v>0</v>
-      </c>
-      <c r="F37" s="19">
-        <v>0</v>
-      </c>
-      <c r="G37" s="19">
-        <v>0</v>
-      </c>
-      <c r="H37" s="19">
-        <v>0</v>
-      </c>
-      <c r="I37" s="19">
-        <v>0</v>
-      </c>
-      <c r="J37" s="19">
-        <v>0</v>
-      </c>
-      <c r="K37" s="19">
-        <v>0</v>
-      </c>
-      <c r="L37" s="19">
-        <v>0</v>
-      </c>
-      <c r="M37" s="19">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
-        <v>0</v>
-      </c>
-      <c r="P37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="19">
-        <v>0</v>
-      </c>
-      <c r="R37" s="19">
-        <v>0</v>
-      </c>
-      <c r="S37" s="19">
-        <v>0</v>
-      </c>
-      <c r="T37" s="19">
-        <v>0</v>
-      </c>
-      <c r="U37" s="19">
-        <v>0</v>
-      </c>
-      <c r="V37" s="19">
-        <v>0</v>
-      </c>
-      <c r="W37" s="19">
-        <v>0</v>
-      </c>
-      <c r="X37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR37" s="19">
+      <c r="C37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D37" s="18">
+        <v>0</v>
+      </c>
+      <c r="E37" s="18">
+        <v>0</v>
+      </c>
+      <c r="F37" s="18">
+        <v>0</v>
+      </c>
+      <c r="G37" s="18">
+        <v>0</v>
+      </c>
+      <c r="H37" s="18">
+        <v>0</v>
+      </c>
+      <c r="I37" s="18">
+        <v>0</v>
+      </c>
+      <c r="J37" s="18">
+        <v>0</v>
+      </c>
+      <c r="K37" s="18">
+        <v>0</v>
+      </c>
+      <c r="L37" s="18">
+        <v>0</v>
+      </c>
+      <c r="M37" s="18">
+        <v>0</v>
+      </c>
+      <c r="N37" s="18">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18">
+        <v>0</v>
+      </c>
+      <c r="P37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>0</v>
+      </c>
+      <c r="R37" s="18">
+        <v>0</v>
+      </c>
+      <c r="S37" s="18">
+        <v>0</v>
+      </c>
+      <c r="T37" s="18">
+        <v>0</v>
+      </c>
+      <c r="U37" s="18">
+        <v>0</v>
+      </c>
+      <c r="V37" s="18">
+        <v>0</v>
+      </c>
+      <c r="W37" s="18">
+        <v>0</v>
+      </c>
+      <c r="X37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>3</v>
+      <c r="A38" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="19">
-        <v>0</v>
-      </c>
-      <c r="E38" s="19">
-        <v>0</v>
-      </c>
-      <c r="F38" s="19">
-        <v>0</v>
-      </c>
-      <c r="G38" s="19">
-        <v>0</v>
-      </c>
-      <c r="H38" s="19">
-        <v>0</v>
-      </c>
-      <c r="I38" s="19">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19">
-        <v>0</v>
-      </c>
-      <c r="K38" s="19">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19">
-        <v>0</v>
-      </c>
-      <c r="M38" s="19">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="19">
-        <v>0</v>
-      </c>
-      <c r="R38" s="19">
-        <v>0</v>
-      </c>
-      <c r="S38" s="19">
-        <v>0</v>
-      </c>
-      <c r="T38" s="19">
-        <v>0</v>
-      </c>
-      <c r="U38" s="19">
-        <v>0</v>
-      </c>
-      <c r="V38" s="19">
-        <v>0</v>
-      </c>
-      <c r="W38" s="19">
-        <v>0</v>
-      </c>
-      <c r="X38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ38" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR38" s="19">
+        <v>7</v>
+      </c>
+      <c r="D38" s="18">
+        <v>0</v>
+      </c>
+      <c r="E38" s="18">
+        <v>0</v>
+      </c>
+      <c r="F38" s="18">
+        <v>0</v>
+      </c>
+      <c r="G38" s="18">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>0</v>
+      </c>
+      <c r="I38" s="18">
+        <v>0</v>
+      </c>
+      <c r="J38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="18">
+        <v>0</v>
+      </c>
+      <c r="L38" s="18">
+        <v>0</v>
+      </c>
+      <c r="M38" s="18">
+        <v>0</v>
+      </c>
+      <c r="N38" s="18">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18">
+        <v>0</v>
+      </c>
+      <c r="P38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>0</v>
+      </c>
+      <c r="R38" s="18">
+        <v>0</v>
+      </c>
+      <c r="S38" s="18">
+        <v>0</v>
+      </c>
+      <c r="T38" s="18">
+        <v>0</v>
+      </c>
+      <c r="U38" s="18">
+        <v>0</v>
+      </c>
+      <c r="V38" s="18">
+        <v>0</v>
+      </c>
+      <c r="W38" s="18">
+        <v>0</v>
+      </c>
+      <c r="X38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>10</v>
@@ -51414,127 +51410,127 @@
       <c r="C39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="19">
-        <v>0</v>
-      </c>
-      <c r="E39" s="19">
-        <v>0</v>
-      </c>
-      <c r="F39" s="19">
-        <v>0</v>
-      </c>
-      <c r="G39" s="19">
-        <v>0</v>
-      </c>
-      <c r="H39" s="19">
-        <v>0</v>
-      </c>
-      <c r="I39" s="19">
-        <v>0</v>
-      </c>
-      <c r="J39" s="19">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19">
-        <v>0</v>
-      </c>
-      <c r="L39" s="19">
-        <v>0</v>
-      </c>
-      <c r="M39" s="19">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
-        <v>0</v>
-      </c>
-      <c r="P39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="19">
-        <v>0</v>
-      </c>
-      <c r="R39" s="19">
-        <v>0</v>
-      </c>
-      <c r="S39" s="19">
-        <v>0</v>
-      </c>
-      <c r="T39" s="19">
-        <v>0</v>
-      </c>
-      <c r="U39" s="19">
-        <v>0</v>
-      </c>
-      <c r="V39" s="19">
-        <v>0</v>
-      </c>
-      <c r="W39" s="19">
-        <v>0</v>
-      </c>
-      <c r="X39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AC39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AE39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AJ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AL39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AM39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AN39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AO39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AQ39" s="19">
-        <v>0</v>
-      </c>
-      <c r="AR39" s="19">
+      <c r="D39" s="18">
+        <v>0</v>
+      </c>
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+      <c r="F39" s="18">
+        <v>0</v>
+      </c>
+      <c r="G39" s="18">
+        <v>0</v>
+      </c>
+      <c r="H39" s="18">
+        <v>0</v>
+      </c>
+      <c r="I39" s="18">
+        <v>0</v>
+      </c>
+      <c r="J39" s="18">
+        <v>0</v>
+      </c>
+      <c r="K39" s="18">
+        <v>0</v>
+      </c>
+      <c r="L39" s="18">
+        <v>0</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0</v>
+      </c>
+      <c r="N39" s="18">
+        <v>0</v>
+      </c>
+      <c r="O39" s="18">
+        <v>0</v>
+      </c>
+      <c r="P39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="18">
+        <v>0</v>
+      </c>
+      <c r="R39" s="18">
+        <v>0</v>
+      </c>
+      <c r="S39" s="18">
+        <v>0</v>
+      </c>
+      <c r="T39" s="18">
+        <v>0</v>
+      </c>
+      <c r="U39" s="18">
+        <v>0</v>
+      </c>
+      <c r="V39" s="18">
+        <v>0</v>
+      </c>
+      <c r="W39" s="18">
+        <v>0</v>
+      </c>
+      <c r="X39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ39" s="18">
+        <v>0</v>
+      </c>
+      <c r="AR39" s="18">
         <v>0</v>
       </c>
     </row>
